--- a/samples/Sample_Payslips.xlsx
+++ b/samples/Sample_Payslips.xlsx
@@ -400,11 +400,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="2" max="2" width="44.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,9 +550,31 @@
         <v>Optional. Free text printed at the bottom of each payslip. Example: This is a system-generated payslip and does not require a signature.</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Logo</v>
+      </c>
+      <c r="B14" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Stamp / Signature</v>
+      </c>
+      <c r="B15" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Optional. The second picture on this sheet is used as the stamp or signature.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2520,7 +2542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -2545,85 +2567,76 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2. Fill the "Payslips" sheet with one row per employee. Delete the example row.</v>
+        <v>2. Optional: insert your logo picture on the "Settings" sheet (Insert &gt; Pictures). A second picture is used as stamp/signature.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. Keep the header row exactly as it is. You may delete optional columns you do not use.</v>
+        <v>3. Fill the "Payslips" sheet with one row per employee. Delete the example row.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>4. Amounts must be numbers (no text). Leave a cell empty for zero.</v>
+        <v>4. Keep the header row. You may delete optional columns you do not use, and reorder columns freely.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>5. Extra pay items: add a column named "Earning: &lt;name&gt;" (e.g. "Earning: Site Allowance").</v>
+        <v>5. Amounts must be numbers (no text). Leave a cell empty for zero.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6. Extra deductions: add a column named "Deduction: &lt;name&gt;" (e.g. "Deduction: Housing Loan").</v>
+        <v>6. Extra pay items: add a column named "Earning: &lt;name&gt;" (e.g. "Earning: Site Allowance").</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>7. Net Salary is calculated automatically (earnings - deductions). If you fill the Net Salary column it is only used as a cross-check.</v>
+        <v>7. Extra deductions: add a column named "Deduction: &lt;name&gt;" (e.g. "Deduction: Housing Loan").</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>8. Save the file, open the Payslip Generator page, upload this file, review the checks, pick a design and export the PDFs.</v>
+        <v>8. Net Salary is calculated automatically (earnings - deductions). If you fill the Net Salary column it is only used as a cross-check.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
+        <v>9. Save the file, open the Payslip Generator page, upload this file, review the checks, pick a design and export the PDFs.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>10. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>COLUMNS</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Required</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Group</v>
+        <v>COLUMNS</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Employee ID</v>
+        <v>Column</v>
       </c>
       <c r="B15" t="str">
-        <v>Yes</v>
+        <v>Required</v>
       </c>
       <c r="C15" t="str">
-        <v>text</v>
+        <v>Type</v>
       </c>
       <c r="D15" t="str">
-        <v>info</v>
+        <v>Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Employee Name</v>
+        <v>Employee ID</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -2637,10 +2650,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>National ID / Iqama</v>
+        <v>Employee Name</v>
       </c>
       <c r="B17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C17" t="str">
         <v>text</v>
@@ -2651,7 +2664,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nationality</v>
+        <v>National ID / Iqama</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -2665,7 +2678,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Job Title</v>
+        <v>Nationality</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -2679,7 +2692,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Department</v>
+        <v>Job Title</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -2693,13 +2706,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Joining Date</v>
+        <v>Department</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>date</v>
+        <v>text</v>
       </c>
       <c r="D21" t="str">
         <v>info</v>
@@ -2707,13 +2720,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bank Name</v>
+        <v>Joining Date</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D22" t="str">
         <v>info</v>
@@ -2721,7 +2734,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>IBAN</v>
+        <v>Bank Name</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -2735,21 +2748,21 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Working Days</v>
+        <v>IBAN</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D24" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Absent Days</v>
+        <v>Working Days</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
@@ -2763,7 +2776,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Overtime Hours</v>
+        <v>Absent Days</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -2777,24 +2790,24 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Basic Salary</v>
+        <v>Overtime Hours</v>
       </c>
       <c r="B27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D27" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Housing Allowance</v>
+        <v>Basic Salary</v>
       </c>
       <c r="B28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C28" t="str">
         <v>money</v>
@@ -2805,7 +2818,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Transport Allowance</v>
+        <v>Housing Allowance</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -2819,7 +2832,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Food Allowance</v>
+        <v>Transport Allowance</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -2833,7 +2846,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Overtime Pay</v>
+        <v>Food Allowance</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -2847,7 +2860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Other Earnings</v>
+        <v>Overtime Pay</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -2861,7 +2874,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GOSI Deduction</v>
+        <v>Other Earnings</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -2870,12 +2883,12 @@
         <v>money</v>
       </c>
       <c r="D33" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Absence Deduction</v>
+        <v>GOSI Deduction</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -2889,7 +2902,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Loan / Advance</v>
+        <v>Absence Deduction</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -2903,7 +2916,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Other Deductions</v>
+        <v>Loan / Advance</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -2917,7 +2930,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Net Salary</v>
+        <v>Other Deductions</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -2926,26 +2939,40 @@
         <v>money</v>
       </c>
       <c r="D37" t="str">
-        <v>check</v>
+        <v>deduction</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Remarks</v>
+        <v>Net Salary</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
+        <v>money</v>
+      </c>
+      <c r="D38" t="str">
+        <v>check</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+      <c r="C39" t="str">
         <v>text</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D39" t="str">
         <v>info</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Sample_Payslips.xlsx
+++ b/samples/Sample_Payslips.xlsx
@@ -2607,7 +2607,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>10. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
+        <v>10. Names and text can be in English or Arabic (or both).</v>
       </c>
     </row>
     <row r="13">

--- a/samples/Sample_Payslips.xlsx
+++ b/samples/Sample_Payslips.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -552,61 +552,122 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Logo</v>
+        <v>Default Country Code</v>
       </c>
       <c r="B14" t="str">
-        <v>(optional: insert the picture anywhere on this sheet)</v>
+        <v>966</v>
       </c>
       <c r="C14" t="str">
-        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+        <v>Optional. Added to mobile numbers written without a country code (966 = Saudi Arabia). Example: 966</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Sender Email</v>
+      </c>
+      <c r="B15" t="str">
+        <v>payroll@example.com</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Optional. The From address used in Outlook drafts and mail-merge files. Example: payroll@example.com</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Message Subject</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Payslip {period} - {company}</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Optional. Subject line for emails and first line of WhatsApp messages. Placeholders: {name} {period} {company} {net} {password_hint} Example: Payslip {period} - {company}</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>Message Text</v>
+      </c>
+      <c r="B17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear {name}, your payslip for {period} is attached. {password_hint}
+This document contains personal data; please do not forward it.
+عزيزي {name}، مرفق قسيمة راتبك لشهر {period}. {password_hint_ar}
+هذا المستند يحتوي على بيانات شخصية، يرجى عدم مشاركته.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Password Rule</v>
+      </c>
+      <c r="B18" t="str">
+        <v>id+dob</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Optional. How each PDF password is built: none, id (National ID / Iqama), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column). Example: id+dob</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Logo</v>
+      </c>
+      <c r="B19" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>Stamp / Signature</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B20" t="str">
         <v>(optional: insert the picture anywhere on this sheet)</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C20" t="str">
         <v>Optional. The second picture on this sheet is used as the stamp or signature.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:AA26"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="21.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" customWidth="1"/>
     <col min="19" max="19" width="16.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
     <col min="21" max="21" width="16.83203125" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="16.83203125" customWidth="1"/>
+    <col min="23" max="23" width="19.83203125" customWidth="1"/>
+    <col min="24" max="24" width="16.83203125" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,63 +684,72 @@
         <v>Nationality</v>
       </c>
       <c r="E1" t="str">
+        <v>Date of Birth</v>
+      </c>
+      <c r="F1" t="str">
         <v>Job Title</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Department</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Joining Date</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>Mobile</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="K1" t="str">
         <v>Bank Name</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>IBAN</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Working Days</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Absent Days</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>Overtime Hours</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Basic Salary</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Housing Allowance</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Transport Allowance</v>
       </c>
-      <c r="P1" t="str">
+      <c r="S1" t="str">
         <v>Food Allowance</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <v>Overtime Pay</v>
       </c>
-      <c r="R1" t="str">
+      <c r="U1" t="str">
         <v>Other Earnings</v>
       </c>
-      <c r="S1" t="str">
+      <c r="V1" t="str">
         <v>GOSI Deduction</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
         <v>Absence Deduction</v>
       </c>
-      <c r="U1" t="str">
+      <c r="X1" t="str">
         <v>Loan / Advance</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Y1" t="str">
         <v>Other Deductions</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <v>Net Salary</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <v>Remarks</v>
       </c>
     </row>
@@ -696,64 +766,73 @@
       <c r="D2" t="str">
         <v>Saudi</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2" s="1">
+        <v>27395</v>
+      </c>
+      <c r="F2" t="str">
         <v>Site Engineer</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Projects</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>44562</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v>0550000000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>ahmed.hassan1@example.com</v>
+      </c>
+      <c r="K2" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I2" t="str">
+      <c r="L2" t="str">
         <v>SA1000000000200000000000</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>28</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>3000</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>750</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>300</v>
       </c>
-      <c r="P2">
+      <c r="S2">
         <v>300</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
         <v>365.63</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <v>270</v>
       </c>
-      <c r="U2">
+      <c r="X2">
         <v>500</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
         <v>Includes overtime for site work</v>
       </c>
     </row>
@@ -770,64 +849,73 @@
       <c r="D3" t="str">
         <v>Egyptian</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3" s="1">
+        <v>27915</v>
+      </c>
+      <c r="F3" t="str">
         <v>Foreman</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Operations</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>44959</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
+        <v>0550007919</v>
+      </c>
+      <c r="J3" t="str">
+        <v>mohammed.kumar2@example.com</v>
+      </c>
+      <c r="K3" t="str">
         <v>SNB</v>
       </c>
-      <c r="I3" t="str">
+      <c r="L3" t="str">
         <v>SA1000987654200000012345</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>30</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
         <v>7</v>
       </c>
-      <c r="M3">
+      <c r="P3">
         <v>3937</v>
       </c>
-      <c r="N3">
+      <c r="Q3">
         <v>984</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <v>350</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>172.24</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
         <v/>
       </c>
     </row>
@@ -844,64 +932,73 @@
       <c r="D4" t="str">
         <v>Indian</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" s="1">
+        <v>28436</v>
+      </c>
+      <c r="F4" t="str">
         <v>Electrician</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Finance</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>45354</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
+        <v>0550015838</v>
+      </c>
+      <c r="J4" t="str">
+        <v>fatima.ibrahim3@example.com</v>
+      </c>
+      <c r="K4" t="str">
         <v>Riyad Bank</v>
       </c>
-      <c r="I4" t="str">
+      <c r="L4" t="str">
         <v>SA1001975308200000024690</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>30</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>14</v>
       </c>
-      <c r="M4">
+      <c r="P4">
         <v>4874</v>
       </c>
-      <c r="N4">
+      <c r="Q4">
         <v>1219</v>
       </c>
-      <c r="O4">
+      <c r="R4">
         <v>400</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>426.48</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
         <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
-      <c r="W4" t="str">
-        <v/>
-      </c>
-      <c r="X4" t="str">
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
         <v/>
       </c>
     </row>
@@ -918,64 +1015,73 @@
       <c r="D5" t="str">
         <v>Pakistani</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" s="1">
+        <v>28590</v>
+      </c>
+      <c r="F5" t="str">
         <v>Driver</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>HSE</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>45751</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
+        <v>0550023757</v>
+      </c>
+      <c r="J5" t="str">
+        <v>rajesh.youssef4@example.com</v>
+      </c>
+      <c r="K5" t="str">
         <v>Alinma Bank</v>
       </c>
-      <c r="I5" t="str">
+      <c r="L5" t="str">
         <v>SA1002962962200000037035</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>30</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>21</v>
       </c>
-      <c r="M5">
+      <c r="P5">
         <v>5811</v>
       </c>
-      <c r="N5">
+      <c r="Q5">
         <v>1453</v>
       </c>
-      <c r="O5">
+      <c r="R5">
         <v>450</v>
       </c>
-      <c r="P5">
+      <c r="S5">
         <v>300</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>762.69</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
         <v/>
       </c>
     </row>
@@ -992,64 +1098,73 @@
       <c r="D6" t="str">
         <v>Filipino</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" s="1">
+        <v>29111</v>
+      </c>
+      <c r="F6" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Administration</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>44686</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
+        <v>0550031676</v>
+      </c>
+      <c r="J6" t="str">
+        <v>maria.reyes5@example.com</v>
+      </c>
+      <c r="K6" t="str">
         <v>Bank Albilad</v>
       </c>
-      <c r="I6" t="str">
+      <c r="L6" t="str">
         <v>SA1003950616200000049380</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>30</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="M6">
+      <c r="P6">
         <v>6748</v>
       </c>
-      <c r="N6">
+      <c r="Q6">
         <v>1687</v>
       </c>
-      <c r="O6">
+      <c r="R6">
         <v>500</v>
       </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>126.53</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
-      <c r="W6" t="str">
-        <v/>
-      </c>
-      <c r="X6" t="str">
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
         <v/>
       </c>
     </row>
@@ -1066,64 +1181,73 @@
       <c r="D7" t="str">
         <v>Bangladeshi</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" s="1">
+        <v>29267</v>
+      </c>
+      <c r="F7" t="str">
         <v>Safety Officer</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>Projects</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>45083</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
+        <v>0550039595</v>
+      </c>
+      <c r="J7" t="str">
+        <v>john.patel6@example.com</v>
+      </c>
+      <c r="K7" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I7" t="str">
+      <c r="L7" t="str">
         <v>SA1004938270200000061725</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>30</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>10</v>
       </c>
-      <c r="M7">
+      <c r="P7">
         <v>7685</v>
       </c>
-      <c r="N7">
+      <c r="Q7">
         <v>1921</v>
       </c>
-      <c r="O7">
+      <c r="R7">
         <v>550</v>
       </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>480.31</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
-      <c r="W7" t="str">
-        <v/>
-      </c>
-      <c r="X7" t="str">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
         <v/>
       </c>
     </row>
@@ -1140,64 +1264,73 @@
       <c r="D8" t="str">
         <v>Sudanese</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8" s="1">
+        <v>29786</v>
+      </c>
+      <c r="F8" t="str">
         <v>Mason</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>Operations</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>45480</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
+        <v>0550047514</v>
+      </c>
+      <c r="J8" t="str">
+        <v>khalid.okafor7@example.com</v>
+      </c>
+      <c r="K8" t="str">
         <v>SNB</v>
       </c>
-      <c r="I8" t="str">
+      <c r="L8" t="str">
         <v>SA1005925924200000074070</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>30</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>17</v>
       </c>
-      <c r="M8">
+      <c r="P8">
         <v>8622</v>
       </c>
-      <c r="N8">
+      <c r="Q8">
         <v>2156</v>
       </c>
-      <c r="O8">
+      <c r="R8">
         <v>600</v>
       </c>
-      <c r="P8">
+      <c r="S8">
         <v>300</v>
       </c>
-      <c r="Q8">
+      <c r="T8">
         <v>916.09</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
-      <c r="W8" t="str">
-        <v/>
-      </c>
-      <c r="X8" t="str">
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
         <v/>
       </c>
     </row>
@@ -1214,64 +1347,73 @@
       <c r="D9" t="str">
         <v>Jordanian</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" s="1">
+        <v>30307</v>
+      </c>
+      <c r="F9" t="str">
         <v>Surveyor</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Finance</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>45877</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
+        <v>0550055433</v>
+      </c>
+      <c r="J9" t="str">
+        <v>priya.alotaibi8@example.com</v>
+      </c>
+      <c r="K9" t="str">
         <v>Riyad Bank</v>
       </c>
-      <c r="I9" t="str">
+      <c r="L9" t="str">
         <v>SA1006913578200000086415</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>30</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>24</v>
       </c>
-      <c r="M9">
+      <c r="P9">
         <v>9559</v>
       </c>
-      <c r="N9">
+      <c r="Q9">
         <v>2390</v>
       </c>
-      <c r="O9">
+      <c r="R9">
         <v>650</v>
       </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>1433.85</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
         <v>500</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9" t="str">
-        <v/>
-      </c>
-      <c r="X9" t="str">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
         <v/>
       </c>
     </row>
@@ -1288,64 +1430,73 @@
       <c r="D10" t="str">
         <v>Saudi</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" s="1">
+        <v>30461</v>
+      </c>
+      <c r="F10" t="str">
         <v>HR Officer</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>HSE</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>44813</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
+        <v>0550063352</v>
+      </c>
+      <c r="J10" t="str">
+        <v>omar.santos9@example.com</v>
+      </c>
+      <c r="K10" t="str">
         <v>Alinma Bank</v>
       </c>
-      <c r="I10" t="str">
+      <c r="L10" t="str">
         <v>SA1007901232200000098760</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>30</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
         <v>6</v>
       </c>
-      <c r="M10">
+      <c r="P10">
         <v>10496</v>
       </c>
-      <c r="N10">
+      <c r="Q10">
         <v>2624</v>
       </c>
-      <c r="O10">
+      <c r="R10">
         <v>300</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>393.6</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>1279.2</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10" t="str">
-        <v/>
-      </c>
-      <c r="X10" t="str">
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
         <v/>
       </c>
     </row>
@@ -1362,64 +1513,73 @@
       <c r="D11" t="str">
         <v>Egyptian</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11" s="1">
+        <v>30983</v>
+      </c>
+      <c r="F11" t="str">
         <v>Plumber</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Administration</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>45209</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
+        <v>0550071271</v>
+      </c>
+      <c r="J11" t="str">
+        <v>sara.sharma10@example.com</v>
+      </c>
+      <c r="K11" t="str">
         <v>Bank Albilad</v>
       </c>
-      <c r="I11" t="str">
+      <c r="L11" t="str">
         <v>SA1008888886200000111105</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>30</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>13</v>
       </c>
-      <c r="M11">
+      <c r="P11">
         <v>11433</v>
       </c>
-      <c r="N11">
+      <c r="Q11">
         <v>2858</v>
       </c>
-      <c r="O11">
+      <c r="R11">
         <v>350</v>
       </c>
-      <c r="P11">
+      <c r="S11">
         <v>300</v>
       </c>
-      <c r="Q11">
+      <c r="T11">
         <v>928.93</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
-      <c r="W11" t="str">
-        <v/>
-      </c>
-      <c r="X11" t="str">
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
         <v>Includes overtime for site work</v>
       </c>
     </row>
@@ -1436,64 +1596,73 @@
       <c r="D12" t="str">
         <v>Indian</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12" s="1">
+        <v>31109</v>
+      </c>
+      <c r="F12" t="str">
         <v>Site Engineer</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>Projects</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>45607</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
+        <v>0550079190</v>
+      </c>
+      <c r="J12" t="str">
+        <v>ali.rahman11@example.com</v>
+      </c>
+      <c r="K12" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I12" t="str">
+      <c r="L12" t="str">
         <v>SA1009876540200000123450</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>30</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>20</v>
       </c>
-      <c r="M12">
+      <c r="P12">
         <v>3370</v>
       </c>
-      <c r="N12">
+      <c r="Q12">
         <v>843</v>
       </c>
-      <c r="O12">
+      <c r="R12">
         <v>400</v>
       </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>421.25</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
         <v>0</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
-      <c r="W12" t="str">
-        <v/>
-      </c>
-      <c r="X12" t="str">
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
         <v/>
       </c>
     </row>
@@ -1510,64 +1679,73 @@
       <c r="D13" t="str">
         <v>Pakistani</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13" s="1">
+        <v>31630</v>
+      </c>
+      <c r="F13" t="str">
         <v>Foreman</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>Operations</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>46003</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
+        <v>0550087109</v>
+      </c>
+      <c r="J13" t="str">
+        <v>noor.malik12@example.com</v>
+      </c>
+      <c r="K13" t="str">
         <v>SNB</v>
       </c>
-      <c r="I13" t="str">
+      <c r="L13" t="str">
         <v>SA1010864194200000135795</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>28</v>
       </c>
-      <c r="K13">
+      <c r="N13">
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="M13">
+      <c r="P13">
         <v>4307</v>
       </c>
-      <c r="N13">
+      <c r="Q13">
         <v>1077</v>
       </c>
-      <c r="O13">
+      <c r="R13">
         <v>450</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>53.84</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
         <v>388.93</v>
       </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13" t="str">
-        <v/>
-      </c>
-      <c r="X13" t="str">
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
         <v/>
       </c>
     </row>
@@ -1584,64 +1762,73 @@
       <c r="D14" t="str">
         <v>Filipino</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" s="1">
+        <v>31786</v>
+      </c>
+      <c r="F14" t="str">
         <v>Electrician</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Finance</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>44574</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
+        <v>0550095028</v>
+      </c>
+      <c r="J14" t="str">
+        <v>carlos.haddad13@example.com</v>
+      </c>
+      <c r="K14" t="str">
         <v>Riyad Bank</v>
       </c>
-      <c r="I14" t="str">
+      <c r="L14" t="str">
         <v>SA1011851848200000148140</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>30</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>9</v>
       </c>
-      <c r="M14">
+      <c r="P14">
         <v>5244</v>
       </c>
-      <c r="N14">
+      <c r="Q14">
         <v>1311</v>
       </c>
-      <c r="O14">
+      <c r="R14">
         <v>500</v>
       </c>
-      <c r="P14">
+      <c r="S14">
         <v>300</v>
       </c>
-      <c r="Q14">
+      <c r="T14">
         <v>294.98</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
         <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-      <c r="X14" t="str">
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
         <v/>
       </c>
     </row>
@@ -1658,64 +1845,73 @@
       <c r="D15" t="str">
         <v>Bangladeshi</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15" s="1">
+        <v>32306</v>
+      </c>
+      <c r="F15" t="str">
         <v>Driver</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>HSE</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>44971</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
+        <v>0550102947</v>
+      </c>
+      <c r="J15" t="str">
+        <v>aisha.aziz14@example.com</v>
+      </c>
+      <c r="K15" t="str">
         <v>Alinma Bank</v>
       </c>
-      <c r="I15" t="str">
+      <c r="L15" t="str">
         <v>SA1012839502200000160485</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>30</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>16</v>
       </c>
-      <c r="M15">
+      <c r="P15">
         <v>6181</v>
       </c>
-      <c r="N15">
+      <c r="Q15">
         <v>1545</v>
       </c>
-      <c r="O15">
+      <c r="R15">
         <v>550</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>618.1</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
         <v>0</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
         <v/>
       </c>
     </row>
@@ -1732,64 +1928,73 @@
       <c r="D16" t="str">
         <v>Sudanese</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16" s="1">
+        <v>32827</v>
+      </c>
+      <c r="F16" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>Administration</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>45366</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
+        <v>0550110866</v>
+      </c>
+      <c r="J16" t="str">
+        <v>hassan.khan15@example.com</v>
+      </c>
+      <c r="K16" t="str">
         <v>Bank Albilad</v>
       </c>
-      <c r="I16" t="str">
+      <c r="L16" t="str">
         <v>SA1013827156200000172830</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>30</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>23</v>
       </c>
-      <c r="M16">
+      <c r="P16">
         <v>7118</v>
       </c>
-      <c r="N16">
+      <c r="Q16">
         <v>1780</v>
       </c>
-      <c r="O16">
+      <c r="R16">
         <v>600</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
         <v>1023.21</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
         <v>500</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16" t="str">
-        <v/>
-      </c>
-      <c r="X16" t="str">
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
         <v/>
       </c>
     </row>
@@ -1806,64 +2011,73 @@
       <c r="D17" t="str">
         <v>Jordanian</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17" s="1">
+        <v>32981</v>
+      </c>
+      <c r="F17" t="str">
         <v>Safety Officer</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Projects</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>45763</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
+        <v>0550118785</v>
+      </c>
+      <c r="J17" t="str">
+        <v>deepak.smith16@example.com</v>
+      </c>
+      <c r="K17" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I17" t="str">
+      <c r="L17" t="str">
         <v>SA1014814810200000185175</v>
       </c>
-      <c r="J17">
+      <c r="M17">
         <v>30</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>5</v>
       </c>
-      <c r="M17">
+      <c r="P17">
         <v>8055</v>
       </c>
-      <c r="N17">
+      <c r="Q17">
         <v>2014</v>
       </c>
-      <c r="O17">
+      <c r="R17">
         <v>650</v>
       </c>
-      <c r="P17">
+      <c r="S17">
         <v>300</v>
       </c>
-      <c r="Q17">
+      <c r="T17">
         <v>251.72</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
-      <c r="W17" t="str">
-        <v/>
-      </c>
-      <c r="X17" t="str">
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
         <v/>
       </c>
     </row>
@@ -1880,64 +2094,73 @@
       <c r="D18" t="str">
         <v>Saudi</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18" s="1">
+        <v>33502</v>
+      </c>
+      <c r="F18" t="str">
         <v>Mason</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Operations</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>44698</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
+        <v>0550126704</v>
+      </c>
+      <c r="J18" t="str">
+        <v>lina.abdullah17@example.com</v>
+      </c>
+      <c r="K18" t="str">
         <v>SNB</v>
       </c>
-      <c r="I18" t="str">
+      <c r="L18" t="str">
         <v>SA1015802464200000197520</v>
       </c>
-      <c r="J18">
+      <c r="M18">
         <v>30</v>
       </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>12</v>
       </c>
-      <c r="M18">
+      <c r="P18">
         <v>8992</v>
       </c>
-      <c r="N18">
+      <c r="Q18">
         <v>2248</v>
       </c>
-      <c r="O18">
+      <c r="R18">
         <v>300</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
         <v>674.4</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>1095.9</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18" t="str">
-        <v/>
-      </c>
-      <c r="X18" t="str">
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
         <v/>
       </c>
     </row>
@@ -1954,64 +2177,73 @@
       <c r="D19" t="str">
         <v>Egyptian</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19" s="1">
+        <v>33658</v>
+      </c>
+      <c r="F19" t="str">
         <v>Surveyor</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>Finance</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>45095</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
+        <v>0550134623</v>
+      </c>
+      <c r="J19" t="str">
+        <v>yusuf.siddiqui18@example.com</v>
+      </c>
+      <c r="K19" t="str">
         <v>Riyad Bank</v>
       </c>
-      <c r="I19" t="str">
+      <c r="L19" t="str">
         <v>SA1016790118200000209865</v>
       </c>
-      <c r="J19">
+      <c r="M19">
         <v>30</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>19</v>
       </c>
-      <c r="M19">
+      <c r="P19">
         <v>9929</v>
       </c>
-      <c r="N19">
+      <c r="Q19">
         <v>2482</v>
       </c>
-      <c r="O19">
+      <c r="R19">
         <v>350</v>
       </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>1179.07</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
         <v>0</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
-      <c r="W19" t="str">
-        <v/>
-      </c>
-      <c r="X19" t="str">
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
+      </c>
+      <c r="AA19" t="str">
         <v/>
       </c>
     </row>
@@ -2028,64 +2260,73 @@
       <c r="D20" t="str">
         <v>Indian</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20" s="1">
+        <v>34177</v>
+      </c>
+      <c r="F20" t="str">
         <v>HR Officer</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>HSE</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>45492</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
+        <v>0550142542</v>
+      </c>
+      <c r="J20" t="str">
+        <v>grace.farouk19@example.com</v>
+      </c>
+      <c r="K20" t="str">
         <v>Alinma Bank</v>
       </c>
-      <c r="I20" t="str">
+      <c r="L20" t="str">
         <v>SA1017777772200000222210</v>
       </c>
-      <c r="J20">
+      <c r="M20">
         <v>30</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
         <v>1</v>
       </c>
-      <c r="M20">
+      <c r="P20">
         <v>10866</v>
       </c>
-      <c r="N20">
+      <c r="Q20">
         <v>2717</v>
       </c>
-      <c r="O20">
+      <c r="R20">
         <v>400</v>
       </c>
-      <c r="P20">
+      <c r="S20">
         <v>300</v>
       </c>
-      <c r="Q20">
+      <c r="T20">
         <v>67.91</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
         <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
-      <c r="W20" t="str">
-        <v/>
-      </c>
-      <c r="X20" t="str">
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
+      <c r="AA20" t="str">
         <v>Includes overtime for site work</v>
       </c>
     </row>
@@ -2102,64 +2343,73 @@
       <c r="D21" t="str">
         <v>Pakistani</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21" s="1">
+        <v>34670</v>
+      </c>
+      <c r="F21" t="str">
         <v>Plumber</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>Administration</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>45889</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
+        <v>0550150461</v>
+      </c>
+      <c r="J21" t="str">
+        <v>tariq.mansour20@example.com</v>
+      </c>
+      <c r="K21" t="str">
         <v>Bank Albilad</v>
       </c>
-      <c r="I21" t="str">
+      <c r="L21" t="str">
         <v>SA1018765426200000234555</v>
       </c>
-      <c r="J21">
+      <c r="M21">
         <v>30</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>8</v>
       </c>
-      <c r="M21">
+      <c r="P21">
         <v>11803</v>
       </c>
-      <c r="N21">
+      <c r="Q21">
         <v>2951</v>
       </c>
-      <c r="O21">
+      <c r="R21">
         <v>450</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
         <v>590.15</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
         <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
-      <c r="W21" t="str">
-        <v/>
-      </c>
-      <c r="X21" t="str">
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="str">
+        <v/>
+      </c>
+      <c r="AA21" t="str">
         <v/>
       </c>
     </row>
@@ -2176,64 +2426,73 @@
       <c r="D22" t="str">
         <v>Filipino</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22" s="1">
+        <v>34824</v>
+      </c>
+      <c r="F22" t="str">
         <v>Site Engineer</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>Projects</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>44825</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
+        <v>0550158380</v>
+      </c>
+      <c r="J22" t="str">
+        <v>ahmed.hassan21@example.com</v>
+      </c>
+      <c r="K22" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I22" t="str">
+      <c r="L22" t="str">
         <v>SA1019753080200000246900</v>
       </c>
-      <c r="J22">
+      <c r="M22">
         <v>30</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>15</v>
       </c>
-      <c r="M22">
+      <c r="P22">
         <v>3740</v>
       </c>
-      <c r="N22">
+      <c r="Q22">
         <v>935</v>
       </c>
-      <c r="O22">
+      <c r="R22">
         <v>500</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
         <v>350.63</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
         <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
-      <c r="W22" t="str">
-        <v/>
-      </c>
-      <c r="X22" t="str">
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
+      <c r="AA22" t="str">
         <v/>
       </c>
     </row>
@@ -2250,64 +2509,73 @@
       <c r="D23" t="str">
         <v>Bangladeshi</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23" s="1">
+        <v>35346</v>
+      </c>
+      <c r="F23" t="str">
         <v>Foreman</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>Operations</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>45221</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
+        <v>0550166299</v>
+      </c>
+      <c r="J23" t="str">
+        <v>mohammed.kumar22@example.com</v>
+      </c>
+      <c r="K23" t="str">
         <v>SNB</v>
       </c>
-      <c r="I23" t="str">
+      <c r="L23" t="str">
         <v>SA1020740734200000259245</v>
       </c>
-      <c r="J23">
+      <c r="M23">
         <v>30</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>22</v>
       </c>
-      <c r="M23">
+      <c r="P23">
         <v>4677</v>
       </c>
-      <c r="N23">
+      <c r="Q23">
         <v>1169</v>
       </c>
-      <c r="O23">
+      <c r="R23">
         <v>550</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>300</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>643.09</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
         <v>500</v>
       </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23" t="str">
-        <v/>
-      </c>
-      <c r="X23" t="str">
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="str">
+        <v/>
+      </c>
+      <c r="AA23" t="str">
         <v/>
       </c>
     </row>
@@ -2324,64 +2592,73 @@
       <c r="D24" t="str">
         <v>Sudanese</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E24" s="1">
+        <v>35500</v>
+      </c>
+      <c r="F24" t="str">
         <v>Electrician</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>Finance</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>45619</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
+        <v>0550174218</v>
+      </c>
+      <c r="J24" t="str">
+        <v>fatima.ibrahim23@example.com</v>
+      </c>
+      <c r="K24" t="str">
         <v>Riyad Bank</v>
       </c>
-      <c r="I24" t="str">
+      <c r="L24" t="str">
         <v>SA1021728388200000271590</v>
       </c>
-      <c r="J24">
+      <c r="M24">
         <v>28</v>
       </c>
-      <c r="K24">
+      <c r="N24">
         <v>2</v>
       </c>
-      <c r="L24">
+      <c r="O24">
         <v>4</v>
       </c>
-      <c r="M24">
+      <c r="P24">
         <v>5614</v>
       </c>
-      <c r="N24">
+      <c r="Q24">
         <v>1404</v>
       </c>
-      <c r="O24">
+      <c r="R24">
         <v>600</v>
       </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
         <v>140.35</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
         <v>507.87</v>
       </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="str">
+        <v/>
+      </c>
+      <c r="AA24" t="str">
         <v/>
       </c>
     </row>
@@ -2398,64 +2675,73 @@
       <c r="D25" t="str">
         <v>Jordanian</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E25" s="1">
+        <v>36021</v>
+      </c>
+      <c r="F25" t="str">
         <v>Driver</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>HSE</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>46015</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
+        <v>0550182137</v>
+      </c>
+      <c r="J25" t="str">
+        <v>rajesh.youssef24@example.com</v>
+      </c>
+      <c r="K25" t="str">
         <v>Alinma Bank</v>
       </c>
-      <c r="I25" t="str">
+      <c r="L25" t="str">
         <v>SA1022716042200000283935</v>
       </c>
-      <c r="J25">
+      <c r="M25">
         <v>30</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>11</v>
       </c>
-      <c r="M25">
+      <c r="P25">
         <v>6551</v>
       </c>
-      <c r="N25">
+      <c r="Q25">
         <v>1638</v>
       </c>
-      <c r="O25">
+      <c r="R25">
         <v>650</v>
       </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
         <v>450.38</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
         <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="str">
+        <v/>
+      </c>
+      <c r="AA25" t="str">
         <v/>
       </c>
     </row>
@@ -2472,77 +2758,86 @@
       <c r="D26" t="str">
         <v>Saudi</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E26" s="1">
+        <v>36177</v>
+      </c>
+      <c r="F26" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>Administration</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>44586</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
+        <v>0550190056</v>
+      </c>
+      <c r="J26" t="str">
+        <v>maria.reyes25@example.com</v>
+      </c>
+      <c r="K26" t="str">
         <v>Bank Albilad</v>
       </c>
-      <c r="I26" t="str">
+      <c r="L26" t="str">
         <v>SA1023703696200000296280</v>
       </c>
-      <c r="J26">
+      <c r="M26">
         <v>30</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
         <v>18</v>
       </c>
-      <c r="M26">
+      <c r="P26">
         <v>7488</v>
       </c>
-      <c r="N26">
+      <c r="Q26">
         <v>1872</v>
       </c>
-      <c r="O26">
+      <c r="R26">
         <v>300</v>
       </c>
-      <c r="P26">
+      <c r="S26">
         <v>300</v>
       </c>
-      <c r="Q26">
+      <c r="T26">
         <v>842.4</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
         <v>912.6</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="str">
+        <v/>
+      </c>
+      <c r="AA26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D42"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -2692,13 +2987,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Job Title</v>
+        <v>Date of Birth</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D20" t="str">
         <v>info</v>
@@ -2706,7 +3001,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Department</v>
+        <v>Job Title</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -2720,13 +3015,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Joining Date</v>
+        <v>Department</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>date</v>
+        <v>text</v>
       </c>
       <c r="D22" t="str">
         <v>info</v>
@@ -2734,13 +3029,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bank Name</v>
+        <v>Joining Date</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D23" t="str">
         <v>info</v>
@@ -2748,108 +3043,108 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>IBAN</v>
+        <v>Mobile</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>text</v>
+        <v>phone</v>
       </c>
       <c r="D24" t="str">
-        <v>info</v>
+        <v>contact</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Working Days</v>
+        <v>Email</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>number</v>
+        <v>email</v>
       </c>
       <c r="D25" t="str">
-        <v>attendance</v>
+        <v>contact</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Absent Days</v>
+        <v>Bank Name</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D26" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Overtime Hours</v>
+        <v>IBAN</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D27" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Basic Salary</v>
+        <v>Working Days</v>
       </c>
       <c r="B28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D28" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Housing Allowance</v>
+        <v>Absent Days</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D29" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Transport Allowance</v>
+        <v>Overtime Hours</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D30" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Food Allowance</v>
+        <v>Basic Salary</v>
       </c>
       <c r="B31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C31" t="str">
         <v>money</v>
@@ -2860,7 +3155,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Overtime Pay</v>
+        <v>Housing Allowance</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -2874,7 +3169,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Other Earnings</v>
+        <v>Transport Allowance</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -2888,7 +3183,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GOSI Deduction</v>
+        <v>Food Allowance</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -2897,12 +3192,12 @@
         <v>money</v>
       </c>
       <c r="D34" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Absence Deduction</v>
+        <v>Overtime Pay</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -2911,12 +3206,12 @@
         <v>money</v>
       </c>
       <c r="D35" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Loan / Advance</v>
+        <v>Other Earnings</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -2925,12 +3220,12 @@
         <v>money</v>
       </c>
       <c r="D36" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Other Deductions</v>
+        <v>GOSI Deduction</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -2944,7 +3239,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Net Salary</v>
+        <v>Absence Deduction</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -2953,26 +3248,68 @@
         <v>money</v>
       </c>
       <c r="D38" t="str">
-        <v>check</v>
+        <v>deduction</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Remarks</v>
+        <v>Loan / Advance</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
+        <v>money</v>
+      </c>
+      <c r="D39" t="str">
+        <v>deduction</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="B40" t="str">
+        <v>No</v>
+      </c>
+      <c r="C40" t="str">
+        <v>money</v>
+      </c>
+      <c r="D40" t="str">
+        <v>deduction</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Net Salary</v>
+      </c>
+      <c r="B41" t="str">
+        <v>No</v>
+      </c>
+      <c r="C41" t="str">
+        <v>money</v>
+      </c>
+      <c r="D41" t="str">
+        <v>check</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="B42" t="str">
+        <v>No</v>
+      </c>
+      <c r="C42" t="str">
         <v>text</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D42" t="str">
         <v>info</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Sample_Payslips.xlsx
+++ b/samples/Sample_Payslips.xlsx
@@ -588,10 +588,10 @@
         <v>Message Text</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear {name}, your payslip for {period} is attached. {password_hint}
-This document contains personal data; please do not forward it.
-عزيزي {name}، مرفق قسيمة راتبك لشهر {period}. {password_hint_ar}
-هذا المستند يحتوي على بيانات شخصية، يرجى عدم مشاركته.</v>
+        <v xml:space="preserve">Dear {name},
+Please find attached your payslip for {period}.
+{password_hint}
+{company}</v>
       </c>
       <c r="C17" t="str">
         <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
@@ -602,10 +602,10 @@
         <v>Password Rule</v>
       </c>
       <c r="B18" t="str">
-        <v>id+dob</v>
+        <v>id</v>
       </c>
       <c r="C18" t="str">
-        <v>Optional. How each PDF password is built: none, id (National ID / Iqama), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column). Example: id+dob</v>
+        <v>Optional. PDF password: id (National ID / Iqama number, default), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column), none. Example: id</v>
       </c>
     </row>
     <row r="19">

--- a/samples/Sample_Payslips.xlsx
+++ b/samples/Sample_Payslips.xlsx
@@ -588,13 +588,13 @@
         <v>Message Text</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear {name},
+        <v xml:space="preserve">Dear {first_name},
 Please find attached your payslip for {period}.
 {password_hint}
-{company}</v>
+Best regards</v>
       </c>
       <c r="C17" t="str">
-        <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
+        <v>Optional. Body of the email / WhatsApp message. Placeholders: {first_name} {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
       </c>
     </row>
     <row r="18">
